--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486872_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486872_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2014</v>
+        <v>2.2491</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7191</v>
+        <v>0.7075</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4823</v>
+        <v>1.5416</v>
       </c>
       <c r="G2" t="n">
         <v>0.0271</v>
@@ -610,13 +610,13 @@
         <v>2.2588</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.0368</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2753</v>
+        <v>-0.2869</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1908</v>
+        <v>0.2501</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6193</v>
+        <v>0.6587</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.3086</v>
+        <v>-2.5953</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9279</v>
+        <v>3.2539</v>
       </c>
       <c r="G3" t="n">
         <v>-2.2082</v>
@@ -688,13 +688,13 @@
         <v>4.3122</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2395</v>
+        <v>-1.2001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1663</v>
+        <v>-0.1204</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4058</v>
+        <v>-1.0798</v>
       </c>
       <c r="V3" t="n">
         <v>0.7815</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SALO BLAYA</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.2167</v>
+        <v>-1.3557</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.5701</v>
+        <v>-0.433</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3534</v>
+        <v>-0.9227</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3195</v>
+        <v>1.7109</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6747</v>
+        <v>2.5239</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6449</v>
+        <v>-0.8131</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6269</v>
+        <v>1.2366</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5874</v>
+        <v>2.6313</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0395</v>
+        <v>-1.3947</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6927</v>
+        <v>0.4743</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0873</v>
+        <v>-0.1074</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6054</v>
+        <v>0.5816</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6427</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2153</v>
+        <v>-0.3593</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8832</v>
+        <v>-0.2054</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.1539</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1088</v>
+        <v>-1.8858</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1088</v>
+        <v>-2.4751</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>P. SALO BLAYA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.1932</v>
+        <v>-1.6393</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9444</v>
+        <v>-2.1706</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2488</v>
+        <v>0.5313</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7109</v>
+        <v>1.3195</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5239</v>
+        <v>0.6747</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8131</v>
+        <v>0.6449</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2366</v>
+        <v>0.6269</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6313</v>
+        <v>0.5874</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3947</v>
+        <v>0.0395</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4743</v>
+        <v>0.6927</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1074</v>
+        <v>0.0873</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5816</v>
+        <v>0.6054</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.8214</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1968</v>
+        <v>-0.2073</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7169</v>
+        <v>0.2827</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8858</v>
+        <v>-1.1088</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4751</v>
+        <v>-1.1088</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.4211</v>
+        <v>-2.235</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.1561</v>
+        <v>-2.881</v>
       </c>
       <c r="F6" t="n">
-        <v>0.735</v>
+        <v>0.646</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1127</v>
@@ -922,13 +922,13 @@
         <v>2.8748</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8148</v>
+        <v>-0.6286</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.3446</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8843</v>
+        <v>-0.9732</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2883</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. OKENCHI</t>
+          <t>D. CUELLAR GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9531</v>
+        <v>-2.8089</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.7891</v>
+        <v>-7.677</v>
       </c>
       <c r="F7" t="n">
-        <v>0.836</v>
+        <v>4.8681</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.225</v>
+        <v>-2.995</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1806</v>
+        <v>-1.0742</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0445</v>
+        <v>-1.9208</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0993</v>
+        <v>-3.3335</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0993</v>
+        <v>-1.0833</v>
       </c>
       <c r="L7" t="n">
+        <v>-2.2503</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8214</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-4.1068</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4.9282</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.7050999999999999</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.2366</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.4684</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.0698</v>
+      </c>
+      <c r="W7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>-0.1257</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-0.0813</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.0445</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-2.2588</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-3.0801</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.8214</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.2289</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.0885</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.1404</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.6982</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.6982</v>
-      </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CUELLAR GARCIA</t>
+          <t>O. OKENCHI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4877</v>
+        <v>-3.3897</v>
       </c>
       <c r="E8" t="n">
-        <v>-8.711499999999999</v>
+        <v>-4.2849</v>
       </c>
       <c r="F8" t="n">
-        <v>5.2238</v>
+        <v>0.8953</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.995</v>
+        <v>-1.225</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0742</v>
+        <v>-1.1806</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9208</v>
+        <v>-0.0445</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.3335</v>
+        <v>-1.0993</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0833</v>
+        <v>-1.0993</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.2503</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3385</v>
+        <v>-0.1257</v>
       </c>
       <c r="N8" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.0813</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3295</v>
+        <v>-0.0445</v>
       </c>
       <c r="P8" t="n">
+        <v>-2.2588</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-3.0801</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.8214</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-4.1068</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4.9282</v>
-      </c>
       <c r="S8" t="n">
-        <v>-1.3838</v>
+        <v>0.7923</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2711</v>
+        <v>0.5927</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1127</v>
+        <v>0.1996</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0698</v>
+        <v>-0.6982</v>
       </c>
       <c r="W8" t="n">
+        <v>-0.6982</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.0698</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5588</v>
+        <v>-3.3957</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.0221</v>
+        <v>-5.6812</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4633</v>
+        <v>2.2854</v>
       </c>
       <c r="G9" t="n">
         <v>-4.372</v>
@@ -1156,13 +1156,13 @@
         <v>3.6962</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6029</v>
+        <v>-0.4398</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4574</v>
+        <v>-0.1165</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1454</v>
+        <v>-0.3233</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2267</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.232</v>
+        <v>-4.0079</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.2224</v>
+        <v>-5.6722</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9904</v>
+        <v>1.6643</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1298</v>
@@ -1234,13 +1234,13 @@
         <v>4.1068</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8489</v>
+        <v>-0.6248</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5155999999999999</v>
+        <v>0.0346</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3333</v>
+        <v>-0.6593</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2267</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-17.2419</v>
+        <v>-15.9244</v>
       </c>
       <c r="E11" t="n">
-        <v>-32.0052</v>
+        <v>-30.6877</v>
       </c>
       <c r="F11" t="n">
-        <v>14.7633</v>
+        <v>14.7632</v>
       </c>
       <c r="G11" t="n">
         <v>-9.985199999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.8814</v>
+        <v>-4.881400000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.103800000000001</v>
+        <v>-5.1038</v>
       </c>
       <c r="J11" t="n">
         <v>-12.0991</v>
@@ -1312,13 +1312,13 @@
         <v>25.6679</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.727</v>
+        <v>-3.4095</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0288</v>
+        <v>0.2888000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.6981</v>
+        <v>-3.6982</v>
       </c>
       <c r="V11" t="n">
         <v>-4.583200000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.5383</v>
+        <v>5.0596</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9869</v>
+        <v>0.8823</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5514</v>
+        <v>4.1774</v>
       </c>
       <c r="G12" t="n">
         <v>1.502</v>
@@ -1390,13 +1390,13 @@
         <v>2.6694</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3669</v>
+        <v>0.8882</v>
       </c>
       <c r="T12" t="n">
-        <v>1.104</v>
+        <v>0.9994</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7371</v>
+        <v>-0.1112</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. SANTANA LUCHORO</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9865</v>
+        <v>3.7511</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.108</v>
+        <v>-0.293</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0946</v>
+        <v>4.0441</v>
       </c>
       <c r="G13" t="n">
-        <v>1.746</v>
+        <v>2.6974</v>
       </c>
       <c r="H13" t="n">
-        <v>0.467</v>
+        <v>-0.0391</v>
       </c>
       <c r="I13" t="n">
-        <v>1.279</v>
+        <v>2.7365</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3874</v>
+        <v>1.3258</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4019</v>
+        <v>-0.016</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7893</v>
+        <v>1.3418</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3586</v>
+        <v>1.3716</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8689</v>
+        <v>-0.0231</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4897</v>
+        <v>1.3947</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.6427</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.1068</v>
+        <v>-2.0534</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4641</v>
+        <v>1.8481</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7047</v>
+        <v>0.0804</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4328</v>
+        <v>-0.744</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2719</v>
+        <v>0.8244</v>
       </c>
       <c r="V13" t="n">
         <v>1.1786</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>K. GREELEY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.317</v>
+        <v>3.2386</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3976</v>
+        <v>-0.0144</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7146</v>
+        <v>3.253</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6974</v>
+        <v>0.0803</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0391</v>
+        <v>-1.1063</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7365</v>
+        <v>1.1867</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3258</v>
+        <v>-0.8996</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.016</v>
+        <v>-0.8073</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3418</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3716</v>
+        <v>0.98</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0231</v>
+        <v>-0.299</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3947</v>
+        <v>1.279</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8481</v>
+        <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3537</v>
+        <v>0.185</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8486</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4949</v>
+        <v>0.1929</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1786</v>
+        <v>2.3573</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1786</v>
+        <v>2.9466</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. GREELEY</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3024</v>
+        <v>2.8478</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2236</v>
+        <v>0.347</v>
       </c>
       <c r="F15" t="n">
-        <v>2.526</v>
+        <v>2.5008</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0803</v>
+        <v>1.3587</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1063</v>
+        <v>2.3323</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1867</v>
+        <v>-0.9736</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8996</v>
+        <v>-0.5103</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8073</v>
+        <v>1.4634</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-1.9737</v>
       </c>
       <c r="M15" t="n">
-        <v>0.98</v>
+        <v>1.869</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.299</v>
+        <v>0.8689</v>
       </c>
       <c r="O15" t="n">
-        <v>1.279</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6694</v>
+        <v>2.2588</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7512</v>
+        <v>-0.5724</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2171</v>
+        <v>-0.1241</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5341</v>
+        <v>-0.4483</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3573</v>
+        <v>0.8295</v>
       </c>
       <c r="W15" t="n">
-        <v>2.9466</v>
+        <v>2.0082</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5893</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8202</v>
+        <v>2.7965</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.1088</v>
+        <v>-3.6904</v>
       </c>
       <c r="F16" t="n">
-        <v>5.9291</v>
+        <v>6.4869</v>
       </c>
       <c r="G16" t="n">
         <v>-2.7764</v>
@@ -1702,13 +1702,13 @@
         <v>3.6962</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0504</v>
+        <v>1.0267</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1509</v>
+        <v>0.5693</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1004</v>
+        <v>0.4574</v>
       </c>
       <c r="V16" t="n">
         <v>1.8768</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>J. SANTANA LUCHORO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5342</v>
+        <v>2.604</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3231</v>
+        <v>-1.7817</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8573</v>
+        <v>4.3857</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0697</v>
+        <v>1.746</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7748</v>
+        <v>0.467</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8445</v>
+        <v>1.279</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5403</v>
+        <v>0.3874</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7226</v>
+        <v>-0.4019</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2629</v>
+        <v>0.7893</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5294</v>
+        <v>1.3586</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0522</v>
+        <v>0.8689</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5816</v>
+        <v>0.4897</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.6962</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.1336</v>
+        <v>-4.1068</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4374</v>
+        <v>2.4641</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4624</v>
+        <v>1.3221</v>
       </c>
       <c r="T17" t="n">
-        <v>3.0915</v>
+        <v>0.7592</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3709</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6982</v>
+        <v>1.1786</v>
       </c>
       <c r="W17" t="n">
         <v>1.1786</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3502</v>
+        <v>2.2303</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3852</v>
+        <v>-0.2991</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7354</v>
+        <v>2.5294</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3587</v>
+        <v>4.21</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3323</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9736</v>
+        <v>4.3071</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5103</v>
+        <v>3.4515</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4634</v>
+        <v>0.3996</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9737</v>
+        <v>3.0519</v>
       </c>
       <c r="M18" t="n">
-        <v>1.869</v>
+        <v>0.7585</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8689</v>
+        <v>-0.4967</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>1.2552</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2321</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-4.1068</v>
       </c>
       <c r="R18" t="n">
         <v>2.2588</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.07</v>
+        <v>1.2873</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8563</v>
+        <v>0.3563</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2137</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8295</v>
+        <v>-1.4189</v>
       </c>
       <c r="W18" t="n">
-        <v>2.0082</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0396</v>
+        <v>0.3582</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2405</v>
+        <v>-1.5469</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2801</v>
+        <v>1.9051</v>
       </c>
       <c r="G19" t="n">
-        <v>4.21</v>
+        <v>0.0336</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.4443</v>
       </c>
       <c r="I19" t="n">
-        <v>4.3071</v>
+        <v>-0.4107</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4515</v>
+        <v>-0.9036</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3996</v>
+        <v>-0.5611</v>
       </c>
       <c r="L19" t="n">
-        <v>3.0519</v>
+        <v>-0.3425</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7585</v>
+        <v>0.9372</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4967</v>
+        <v>1.0054</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2552</v>
+        <v>-0.0682</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8481</v>
+        <v>0.4107</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2588</v>
+        <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0965</v>
+        <v>1.0926</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5851</v>
+        <v>0.3834</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6816</v>
+        <v>0.7091</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.302</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1787</v>
+        <v>-1.9968</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8767</v>
+        <v>1.9078</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3976</v>
+        <v>1.0697</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2689</v>
+        <v>-0.7748</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1287</v>
+        <v>1.8445</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8612</v>
+        <v>0.5403</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9402</v>
+        <v>-0.7226</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0789</v>
+        <v>1.2629</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4636</v>
+        <v>0.5294</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6713</v>
+        <v>-0.0522</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2077</v>
+        <v>0.5816</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0267</v>
+        <v>-3.6962</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0534</v>
+        <v>-5.1336</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1223</v>
+        <v>1.8393</v>
       </c>
       <c r="T20" t="n">
-        <v>0.736</v>
+        <v>1.4179</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3864</v>
+        <v>0.4215</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5972</v>
+        <v>-0.2688</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3837</v>
+        <v>-2.4925</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7865</v>
+        <v>2.2236</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0336</v>
+        <v>-0.3976</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4443</v>
+        <v>-0.2689</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4107</v>
+        <v>-0.1287</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9036</v>
+        <v>-0.8612</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5611</v>
+        <v>-0.9402</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3425</v>
+        <v>0.0789</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9372</v>
+        <v>0.4636</v>
       </c>
       <c r="N21" t="n">
-        <v>1.0054</v>
+        <v>0.6713</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0682</v>
+        <v>-0.2077</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1372</v>
+        <v>1.1555</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4534</v>
+        <v>0.4222</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5906</v>
+        <v>0.7333</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7475</v>
+        <v>-1.1025</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4009</v>
+        <v>-3.8779</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6534</v>
+        <v>2.7754</v>
       </c>
       <c r="G22" t="n">
         <v>0.4616</v>
@@ -2170,13 +2170,13 @@
         <v>1.8481</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0386</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8563</v>
+        <v>-0.3333</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8177</v>
+        <v>0.9397</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9384</v>
@@ -2203,28 +2203,28 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>17.2417</v>
+        <v>21.4259</v>
       </c>
       <c r="E23" t="n">
-        <v>-14.7632</v>
+        <v>-14.7634</v>
       </c>
       <c r="F23" t="n">
-        <v>32.0051</v>
+        <v>36.18919999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>9.985300000000001</v>
+        <v>9.985299999999999</v>
       </c>
       <c r="H23" t="n">
         <v>4.881699999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>5.103799999999999</v>
+        <v>5.103800000000001</v>
       </c>
       <c r="J23" t="n">
         <v>-2.1137</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2309999999999998</v>
+        <v>0.2309999999999997</v>
       </c>
       <c r="L23" t="n">
         <v>-2.3449</v>
@@ -2239,7 +2239,7 @@
         <v>7.4485</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.053500000000001</v>
+        <v>-2.0535</v>
       </c>
       <c r="Q23" t="n">
         <v>-25.6676</v>
@@ -2248,16 +2248,16 @@
         <v>23.6144</v>
       </c>
       <c r="S23" t="n">
-        <v>4.726900000000001</v>
+        <v>8.911100000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>3.698399999999999</v>
+        <v>3.6984</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0287</v>
+        <v>5.212700000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>4.583100000000001</v>
+        <v>4.5831</v>
       </c>
       <c r="W23" t="n">
         <v>9.3201</v>
